--- a/Test Data/Reconciliation/target_trades.xlsx
+++ b/Test Data/Reconciliation/target_trades.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Full Name</t>
+          <t>FullName</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
